--- a/output/full_scan/batch_seq3_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq3_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O147"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -739,21 +739,21 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>3060</v>
+        <v>3114</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>銘異</t>
+          <t>好德</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1111.419955186505</v>
+        <v>1121.861334153363</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>37.9</v>
+        <v>47.75</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>70.68640414036913</v>
+        <v>78.37896853102723</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.2538593679149</v>
+        <v>60.53998192601144</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.241995518650475</v>
+        <v>0.7044576954208204</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.7749065719509463</v>
+        <v>0.5698979338708701</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3090</v>
+        <v>3060</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>日電貿</t>
+          <t>銘異</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1110.751553462068</v>
+        <v>1111.419955186505</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>332.5</v>
+        <v>37.9</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>79.06585091597287</v>
+        <v>70.68640414036913</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>48.19868502080318</v>
+        <v>24.2538593679149</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.038146314344309</v>
+        <v>3.241995518650475</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>6.886902241892813</v>
+        <v>0.7749065719509463</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3003</v>
+        <v>3090</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>健和興</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1087.40232284718</v>
+        <v>1110.751553462068</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>332.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>69.22113235511088</v>
+        <v>79.06585091597287</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>32.52537651484371</v>
+        <v>48.19868502080318</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.926394048100325</v>
+        <v>2.038146314344309</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3522770072241448</v>
+        <v>6.886902241892813</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>3044</v>
+        <v>3003</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>健和興</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1041.401927107458</v>
+        <v>1087.40232284718</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>573</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>67.99924057230098</v>
+        <v>69.22113235511088</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25.04575429157041</v>
+        <v>32.52537651484371</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.456841000113962</v>
+        <v>1.926394048100325</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>5.682800791250877</v>
+        <v>0.3522770072241448</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>3014</v>
+        <v>3044</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>聯陽</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1040.156855329482</v>
+        <v>1041.401927107458</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>157.5</v>
+        <v>573</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>64.52367054840829</v>
+        <v>67.99924057230098</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>38.46716151641169</v>
+        <v>25.04575429157041</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.221634667395368</v>
+        <v>1.456841000113962</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.0707706067908198</v>
+        <v>5.682800791250877</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>2483</v>
+        <v>3014</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>百容</t>
+          <t>聯陽</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1025.490400822232</v>
+        <v>1040.156855329482</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>39.65</v>
+        <v>157.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>76.75537726048861</v>
+        <v>64.52367054840829</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>48.15432682392481</v>
+        <v>38.46716151641169</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.649040082223229</v>
+        <v>1.221634667395368</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.8283169282947718</v>
+        <v>0.0707706067908198</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>2472</v>
+        <v>2483</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>百容</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1025.354911676029</v>
+        <v>1025.490400822232</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>402</v>
+        <v>39.65</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>65.18317621080443</v>
+        <v>76.75537726048861</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45.11733246703538</v>
+        <v>48.15432682392481</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.902366115829974</v>
+        <v>1.649040082223229</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-2.80690479410535</v>
+        <v>0.8283169282947718</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>3022</v>
+        <v>2472</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>威強電</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1018.038019406083</v>
+        <v>1025.354911676029</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>84.5</v>
+        <v>402</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>64.52365412922154</v>
+        <v>65.18317621080443</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>38.54533993955351</v>
+        <v>45.11733246703538</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5843649341763921</v>
+        <v>1.902366115829974</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2421413062364279</v>
+        <v>-2.80690479410535</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>2488</v>
+        <v>3022</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>漢平</t>
+          <t>威強電</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1009.23618571858</v>
+        <v>1018.038019406083</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>54.8</v>
+        <v>84.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>64.30259928956846</v>
+        <v>64.52365412922154</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>23.81285419974436</v>
+        <v>38.54533993955351</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.489513956199719</v>
+        <v>0.5843649341763921</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0229031516203504</v>
+        <v>0.2421413062364279</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3002</v>
+        <v>2488</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>歐格</t>
+          <t>漢平</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1004</v>
+        <v>1009.23618571858</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>22.95</v>
+        <v>54.8</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>72.92546540062636</v>
+        <v>64.30259928956846</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>24.54231731384156</v>
+        <v>23.81285419974436</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5.183525271881759</v>
+        <v>1.489513956199719</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.3131094483862705</v>
+        <v>0.0229031516203504</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3008</v>
+        <v>3002</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>歐格</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>989.0318746074026</v>
+        <v>1004</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>5195</v>
+        <v>22.95</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>77.57567527079487</v>
+        <v>72.92546540062636</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>41.57726545419792</v>
+        <v>24.54231731384156</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.11095240802036</v>
+        <v>5.183525271881759</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>113.9979220391862</v>
+        <v>0.3131094483862705</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>2610</v>
+        <v>3008</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>987.4615014331312</v>
+        <v>989.0318746074026</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>22</v>
+        <v>5195</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>74.53783793910148</v>
+        <v>77.57567527079487</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>36.60175030585922</v>
+        <v>41.57726545419792</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.34615014331312</v>
+        <v>1.11095240802036</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2566059774499546</v>
+        <v>113.9979220391862</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>3006</v>
+        <v>2610</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>946.10489725505</v>
+        <v>987.4615014331312</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>237.5</v>
+        <v>22</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>56.88980444284381</v>
+        <v>74.53783793910148</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>25.35142501202638</v>
+        <v>36.60175030585922</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.7136452239486589</v>
+        <v>1.34615014331312</v>
       </c>
       <c r="K18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-1.966379928516109</v>
+        <v>0.2566059774499546</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>3094</v>
+        <v>3006</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>聯傑</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>930.9137751136312</v>
+        <v>946.10489725505</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>38.25</v>
+        <v>237.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>66.09182250132697</v>
+        <v>56.88980444284381</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>27.93377146947892</v>
+        <v>25.35142501202638</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.65805571094654</v>
+        <v>0.7136452239486589</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4976693271205559</v>
+        <v>-1.966379928516109</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>2478</v>
+        <v>3094</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>大毅</t>
+          <t>聯傑</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>926.9459077148068</v>
+        <v>930.9137751136312</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>234</v>
+        <v>38.25</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>90.01516866458171</v>
+        <v>66.09182250132697</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>58.82252480577717</v>
+        <v>27.93377146947892</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.805242028892461</v>
+        <v>1.65805571094654</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>6.899767494383564</v>
+        <v>0.4976693271205559</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>3016</v>
+        <v>2478</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>嘉晶</t>
+          <t>大毅</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>922.4162126517334</v>
+        <v>926.9459077148068</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>126.5</v>
+        <v>234</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.82665798072614</v>
+        <v>90.01516866458171</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28.76811869369832</v>
+        <v>58.82252480577717</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.119268702680414</v>
+        <v>2.805242028892461</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.1928490019487077</v>
+        <v>6.899767494383564</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>2520</v>
+        <v>3016</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>冠德</t>
+          <t>嘉晶</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>902.9603326857268</v>
+        <v>922.4162126517334</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>36.4</v>
+        <v>126.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>69.64855084136003</v>
+        <v>58.82665798072614</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>35.46064944100198</v>
+        <v>28.76811869369832</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.896033268572697</v>
+        <v>1.119268702680414</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.462940341148345</v>
+        <v>-0.1928490019487077</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>2462</v>
+        <v>2520</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>良得電</t>
+          <t>冠德</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>871.3806691596395</v>
+        <v>902.9603326857268</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>25.45</v>
+        <v>36.4</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>65.70547055517167</v>
+        <v>69.64855084136003</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>31.29883556725689</v>
+        <v>35.46064944100198</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7853578379127891</v>
+        <v>2.896033268572697</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.125556762675618</v>
+        <v>0.462940341148345</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>2536</v>
+        <v>2462</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>宏普</t>
+          <t>良得電</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>838.2267776467392</v>
+        <v>871.3806691596395</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>22.35</v>
+        <v>25.45</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>69.23287993472294</v>
+        <v>65.70547055517167</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>33.90252079975458</v>
+        <v>31.29883556725689</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4.922677764673912</v>
+        <v>0.7853578379127891</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.238716881092692</v>
+        <v>0.125556762675618</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>3033</v>
+        <v>2536</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>威健</t>
+          <t>宏普</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>823.6286136805019</v>
+        <v>838.2267776467392</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>49.5</v>
+        <v>22.35</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>55.69831833582811</v>
+        <v>69.23287993472294</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.93813303923754</v>
+        <v>33.90252079975458</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.3630745244965282</v>
+        <v>4.922677764673912</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.605604977651619</v>
+        <v>0.238716881092692</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>2481</v>
+        <v>3033</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>威健</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>821.9518310868714</v>
+        <v>823.6286136805019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>160</v>
+        <v>49.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>62.67702522815037</v>
+        <v>55.69831833582811</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>38.92603726625361</v>
+        <v>32.93813303923754</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.2828639912159267</v>
+        <v>0.3630745244965282</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-1.416675187567207</v>
+        <v>-0.605604977651619</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>敦陽科</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>821.0202558959874</v>
+        <v>821.9518310868714</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>153.5</v>
+        <v>160</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>51.8983796783081</v>
+        <v>62.67702522815037</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>29.75556128993934</v>
+        <v>38.92603726625361</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.972299767274094</v>
+        <v>0.2828639912159267</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-1.222551162953947</v>
+        <v>-1.416675187567207</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3035</v>
+        <v>2480</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>智原</t>
+          <t>敦陽科</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>819.0482997204193</v>
+        <v>821.0202558959874</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>209</v>
+        <v>153.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>58.87848723498053</v>
+        <v>51.8983796783081</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>21.9811445074522</v>
+        <v>29.75556128993934</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7335524662884543</v>
+        <v>0.972299767274094</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.477267626783306</v>
+        <v>-1.222551162953947</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>2501</v>
+        <v>3035</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>國建</t>
+          <t>智原</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>818.3742367905727</v>
+        <v>819.0482997204193</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>26.85</v>
+        <v>209</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>65.83443580727862</v>
+        <v>58.87848723498053</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>39.06434953773658</v>
+        <v>21.9811445074522</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.720833238610354</v>
+        <v>0.7335524662884543</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3634875479985541</v>
+        <v>0.477267626783306</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>2645</v>
+        <v>2501</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>國建</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>814.6929445421963</v>
+        <v>818.3742367905727</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>170</v>
+        <v>26.85</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.33129032298387</v>
+        <v>65.83443580727862</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.54724216063802</v>
+        <v>39.06434953773658</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6553479066955885</v>
+        <v>1.720833238610354</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>2</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.0767232185753052</v>
+        <v>0.3634875479985541</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3019</v>
+        <v>2645</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>亞光</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>795.2373978159686</v>
+        <v>814.6929445421963</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>160.5</v>
+        <v>170</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.8825040586781</v>
+        <v>56.33129032298387</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>23.63916935875524</v>
+        <v>25.54724216063802</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6554113710193313</v>
+        <v>0.6553479066955885</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.6983313032242586</v>
+        <v>-0.0767232185753052</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>2547</v>
+        <v>3019</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>日勝生</t>
+          <t>亞光</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>794.7623260074009</v>
+        <v>795.2373978159686</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>11.2</v>
+        <v>160.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>72.46893666388408</v>
+        <v>59.8825040586781</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>32.28996816440053</v>
+        <v>23.63916935875524</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7762326007400906</v>
+        <v>0.6554113710193313</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0908968321402433</v>
+        <v>0.6983313032242586</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>2527</v>
+        <v>2547</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>宏璟</t>
+          <t>日勝生</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>773.9768475537829</v>
+        <v>794.7623260074009</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>39.8</v>
+        <v>11.2</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>67.13760677138004</v>
+        <v>72.46893666388408</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>27.66588369800785</v>
+        <v>32.28996816440053</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.039526516107323</v>
+        <v>0.7762326007400906</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3742274660297353</v>
+        <v>0.0908968321402433</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3048</v>
+        <v>2527</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>益登</t>
+          <t>宏璟</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>765.4937355298441</v>
+        <v>773.9768475537829</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>73.5</v>
+        <v>39.8</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>63.00180794526131</v>
+        <v>67.13760677138004</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>43.24746352313573</v>
+        <v>27.66588369800785</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5268007417374851</v>
+        <v>2.039526516107323</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.8238932458208303</v>
+        <v>0.3742274660297353</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3059</v>
+        <v>3048</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>華晶科</t>
+          <t>益登</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>762.8627475312896</v>
+        <v>765.4937355298441</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>48.85</v>
+        <v>73.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>60.12866365220902</v>
+        <v>63.00180794526131</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>35.29007980529719</v>
+        <v>43.24746352313573</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.8693619570614314</v>
+        <v>0.5268007417374851</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0041604476047427</v>
+        <v>-0.8238932458208303</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>2460</v>
+        <v>3059</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>建通</t>
+          <t>華晶科</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>760.3104224883541</v>
+        <v>762.8627475312896</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>34.8</v>
+        <v>48.85</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>56.68602967790744</v>
+        <v>60.12866365220902</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>14.72020207564367</v>
+        <v>35.29007980529719</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.639113678627463</v>
+        <v>0.8693619570614314</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.3574374190932892</v>
+        <v>-0.0041604476047427</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3088</v>
+        <v>2460</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>艾訊</t>
+          <t>建通</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>758.6325243401825</v>
+        <v>760.3104224883541</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>145</v>
+        <v>34.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>62.53790716728405</v>
+        <v>56.68602967790744</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>38.25289031429767</v>
+        <v>14.72020207564367</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.049387016021531</v>
+        <v>1.639113678627463</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,11 +2425,11 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.973680483106433</v>
+        <v>0.3574374190932892</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>2495</v>
+        <v>3088</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>普安</t>
+          <t>艾訊</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>710.6988356613472</v>
+        <v>718.6325243401825</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>52.1</v>
+        <v>145</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>59.6672640807937</v>
+        <v>62.53790716728405</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>30.66878869300743</v>
+        <v>38.25289031429767</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.7864515818257557</v>
+        <v>1.049387016021531</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0350198058712361</v>
+        <v>-0.973680483106433</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2859,21 +2859,21 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>2535</v>
+        <v>2495</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>普安</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>708.6905974202269</v>
+        <v>710.6988356613472</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>93.7</v>
+        <v>52.1</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>71.56142801410581</v>
+        <v>59.6672640807937</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46.81371037018207</v>
+        <v>30.66878869300743</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.076413908223141</v>
+        <v>0.7864515818257557</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.9952141799976948</v>
+        <v>-0.0350198058712361</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2912,21 +2912,21 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>3046</v>
+        <v>2535</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>建碁</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>703.272351974966</v>
+        <v>708.6905974202269</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>56.8</v>
+        <v>93.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>53.73125620911239</v>
+        <v>71.56142801410581</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>29.93350373928499</v>
+        <v>46.81371037018207</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6368347852107812</v>
+        <v>1.076413908223141</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.4930829636010967</v>
+        <v>0.9952141799976948</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>2537</v>
+        <v>3093</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>聯上發</t>
+          <t>港建*</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>702.4403623411446</v>
+        <v>705.6190753353815</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>70.69193736737671</v>
+        <v>60.79081206838109</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>37.14117787406239</v>
+        <v>24.84006598654272</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.844036234114457</v>
+        <v>0.5370337234840753</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>1</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.2228344176628963</v>
+        <v>0.7186039004767362</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>3023</v>
+        <v>3046</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>信邦</t>
+          <t>建碁</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>701.9246467952065</v>
+        <v>703.272351974966</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>327.5</v>
+        <v>56.8</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>59.35205761373885</v>
+        <v>53.73125620911239</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.11181114228177</v>
+        <v>29.93350373928499</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.7446925143996493</v>
+        <v>0.6368347852107812</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.9014092191069114</v>
+        <v>-0.4930829636010967</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>2461</v>
+        <v>2537</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>光群雷</t>
+          <t>聯上發</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>701.8817456182111</v>
+        <v>702.4403623411446</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>18.4</v>
+        <v>12</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>55.05178395438411</v>
+        <v>70.69193736737671</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>34.25589251925056</v>
+        <v>37.14117787406239</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.3555980328930599</v>
+        <v>1.844036234114457</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0131473397846322</v>
+        <v>0.2228344176628963</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>3018</v>
+        <v>3023</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>隆銘綠能</t>
+          <t>信邦</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>696.6228465082099</v>
+        <v>701.9246467952065</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>11.9</v>
+        <v>327.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>60.86562622908071</v>
+        <v>59.35205761373885</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.70224752266693</v>
+        <v>17.11181114228177</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.956453420623024</v>
+        <v>0.7446925143996493</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1063682689903501</v>
+        <v>-0.9014092191069114</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>2489</v>
+        <v>2461</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>瑞軒</t>
+          <t>光群雷</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>692.6427706174197</v>
+        <v>701.8817456182111</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>48.15</v>
+        <v>18.4</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>55.60398445159788</v>
+        <v>55.05178395438411</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>14.38413898807503</v>
+        <v>34.25589251925056</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6735977054732116</v>
+        <v>0.3555980328930599</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0893484830799159</v>
+        <v>0.0131473397846322</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>3071</v>
+        <v>3018</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>協禧</t>
+          <t>隆銘綠能</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>690.1332529543097</v>
+        <v>696.6228465082099</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>33.2</v>
+        <v>11.9</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>55.85315207631031</v>
+        <v>60.86562622908071</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>28.27131822820824</v>
+        <v>14.70224752266693</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6492719244344732</v>
+        <v>1.956453420623024</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.0757152069373048</v>
+        <v>0.1063682689903501</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>2546</v>
+        <v>2489</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>根基</t>
+          <t>瑞軒</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>689.4906185551303</v>
+        <v>692.6427706174197</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>96.40000000000001</v>
+        <v>48.15</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>71.71089958539459</v>
+        <v>55.60398445159788</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>35.58113703503821</v>
+        <v>14.38413898807503</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6882772392539804</v>
+        <v>0.6735977054732116</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.7396089095742298</v>
+        <v>-0.0893484830799159</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>3105</v>
+        <v>2546</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>根基</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>687.6644245448166</v>
+        <v>689.4906185551303</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>528</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,29 +3361,29 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>55.89941882175483</v>
+        <v>71.71089958539459</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.26347016480559</v>
+        <v>35.58113703503821</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.331927141886069</v>
+        <v>0.6882772392539804</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.17553058855358</v>
+        <v>0.7396089095742298</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3548,21 +3548,21 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>3093</v>
+        <v>2509</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>港建*</t>
+          <t>全坤建</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>675.6190753353815</v>
+        <v>670.9772301110853</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>65</v>
+        <v>14.55</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>60.79081206838109</v>
+        <v>69.41980226925969</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>24.84006598654272</v>
+        <v>36.79088132119065</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5370337234840753</v>
+        <v>1.052912174314156</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.7186039004767362</v>
+        <v>0.195280186320304</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>2509</v>
+        <v>2486</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>全坤建</t>
+          <t>一詮</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>670.9772301110853</v>
+        <v>669.8847648278861</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>14.55</v>
+        <v>276.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>69.41980226925969</v>
+        <v>58.11503485738853</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>36.79088132119065</v>
+        <v>13.31375889714264</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.052912174314156</v>
+        <v>1.111427811858952</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>3</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.195280186320304</v>
+        <v>-1.771489414254684</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>2486</v>
+        <v>2524</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>一詮</t>
+          <t>京城</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>669.8847648278861</v>
+        <v>666.2444465642128</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>276.5</v>
+        <v>39.25</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>58.11503485738853</v>
+        <v>63.52933170182273</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>13.31375889714264</v>
+        <v>21.47393068330214</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.111427811858952</v>
+        <v>1.22444465642128</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.771489414254684</v>
+        <v>0.5524997473512713</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>2524</v>
+        <v>2453</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>京城</t>
+          <t>凌群</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>666.2444465642128</v>
+        <v>658.7514344110245</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>39.25</v>
+        <v>56.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>63.52933170182273</v>
+        <v>46.36752364159261</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>21.47393068330214</v>
+        <v>25.71314314497124</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.22444465642128</v>
+        <v>0.2666333844372299</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.5524997473512713</v>
+        <v>-0.5352654378510088</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>2453</v>
+        <v>2542</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>凌群</t>
+          <t>興富發</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>658.7514344110245</v>
+        <v>652.0075999662423</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>56.6</v>
+        <v>44.75</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,49 +3785,49 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>46.36752364159261</v>
+        <v>59.92671806916429</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>25.71314314497124</v>
+        <v>34.57759475897403</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2666333844372299</v>
+        <v>1.0197514852981</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.5352654378510088</v>
+        <v>0.0294379076988462</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>2542</v>
+        <v>3071</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>興富發</t>
+          <t>協禧</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>652.0075999662423</v>
+        <v>650.1332529543097</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>44.75</v>
+        <v>33.2</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,29 +3838,29 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>59.92671806916429</v>
+        <v>55.85315207631031</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>34.57759475897403</v>
+        <v>28.27131822820824</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.0197514852981</v>
+        <v>0.6492719244344732</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0294379076988462</v>
+        <v>-0.0757152069373048</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3919,21 +3919,21 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>2949</v>
+        <v>3105</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>欣新網</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>628.6558675200275</v>
+        <v>647.6644245448166</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>528</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,29 +3944,29 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>60.04820586555145</v>
+        <v>55.89941882175483</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.84289247741956</v>
+        <v>14.26347016480559</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.2915676738024454</v>
+        <v>1.331927141886069</v>
       </c>
       <c r="K66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M66" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0435222551002794</v>
+        <v>1.17553058855358</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4184,21 +4184,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>3037</v>
+        <v>2949</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>欣新網</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>584.7265127791399</v>
+        <v>588.6558675200275</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>968</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>54.6233371261976</v>
+        <v>60.04820586555145</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>16.98647967511344</v>
+        <v>14.84289247741956</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8821821016621395</v>
+        <v>0.2915676738024454</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-7.842598059027118</v>
+        <v>-0.0435222551002794</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>2505</v>
+        <v>3037</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>國揚</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>574.5601541226159</v>
+        <v>584.7265127791399</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>18.8</v>
+        <v>968</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>57.83353703538413</v>
+        <v>54.6233371261976</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>31.6089068409423</v>
+        <v>16.98647967511344</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.288462838807844</v>
+        <v>0.8821821016621395</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.09852695182394131</v>
+        <v>-7.842598059027118</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>2606</v>
+        <v>2505</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>國揚</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>573.7676076031064</v>
+        <v>574.5601541226159</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>61.5</v>
+        <v>18.8</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>36.78648703979625</v>
+        <v>57.83353703538413</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.61924427340688</v>
+        <v>31.6089068409423</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.76834334347489</v>
+        <v>1.288462838807844</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>3</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.224603494533416</v>
+        <v>0.09852695182394131</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>2465</v>
+        <v>2606</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>麗臺</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>570.9390915160309</v>
+        <v>573.7676076031064</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.13799330849505</v>
+        <v>36.78648703979625</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>20.49644683419005</v>
+        <v>21.61924427340688</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4465797386580683</v>
+        <v>1.76834334347489</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.687878248944469</v>
+        <v>-1.224603494533416</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>3025</v>
+        <v>2465</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>星通</t>
+          <t>麗臺</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>568.2154698532793</v>
+        <v>570.9390915160309</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>71</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>53.19529133110659</v>
+        <v>51.13799330849505</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>16.72396014633181</v>
+        <v>20.49644683419005</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.2284457834318029</v>
+        <v>0.4465797386580683</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.480721739083543</v>
+        <v>-0.687878248944469</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>3047</v>
+        <v>3025</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>訊舟</t>
+          <t>星通</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>567.7965818022222</v>
+        <v>568.2154698532793</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>16.65</v>
+        <v>71</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>59.65879458374058</v>
+        <v>53.19529133110659</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25.59703352802326</v>
+        <v>16.72396014633181</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>2.810382778911822</v>
+        <v>0.2284457834318029</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.07936541177033921</v>
+        <v>-0.480721739083543</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>3028</v>
+        <v>3047</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>增你強</t>
+          <t>訊舟</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>562.9220728764968</v>
+        <v>567.7965818022222</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>75</v>
+        <v>16.65</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>46.43173614001046</v>
+        <v>59.65879458374058</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>28.70403575854185</v>
+        <v>25.59703352802326</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.9999790090308968</v>
+        <v>2.810382778911822</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.157797102773518</v>
+        <v>0.07936541177033921</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>2476</v>
+        <v>3028</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>增你強</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>562.9037414163735</v>
+        <v>562.9220728764968</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>55.13074059702886</v>
+        <v>46.43173614001046</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>13.27273414466217</v>
+        <v>28.70403575854185</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6005269044896572</v>
+        <v>0.9999790090308968</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.2711566778874252</v>
+        <v>-1.157797102773518</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>3010</v>
+        <v>2476</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>華立</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>562.8891751907089</v>
+        <v>562.9037414163735</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45.56834264709242</v>
+        <v>55.13074059702886</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>16.04679977606245</v>
+        <v>13.27273414466217</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.854328402302191</v>
+        <v>0.6005269044896572</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.8580865921202325</v>
+        <v>-0.2711566778874252</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>2497</v>
+        <v>3010</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>怡利電</t>
+          <t>華立</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>562.3762416152036</v>
+        <v>562.8891751907089</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>60.2</v>
+        <v>131</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>49.24055227286812</v>
+        <v>45.56834264709242</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>32.27367066616607</v>
+        <v>16.04679977606245</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7025941848664666</v>
+        <v>1.854328402302191</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.4090386375367505</v>
+        <v>-0.8580865921202325</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>3066</v>
+        <v>2497</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>李洲</t>
+          <t>怡利電</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>556.0802898783217</v>
+        <v>562.3762416152036</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>21.3</v>
+        <v>60.2</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>54.73468314497952</v>
+        <v>49.24055227286812</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>25.2226773428355</v>
+        <v>32.27367066616607</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6650191096340063</v>
+        <v>0.7025941848664666</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,11 +4757,11 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1184694184130912</v>
+        <v>-0.4090386375367505</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>3081</v>
+        <v>2471</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>資通</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>537.0715395258266</v>
+        <v>536.066294033266</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>2440</v>
+        <v>53.8</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,49 +5004,49 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.52652305533513</v>
+        <v>56.78439422277883</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.1627303013265</v>
+        <v>15.10198851014008</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.943030251383168</v>
+        <v>0.36254739652349</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-33.7363695881854</v>
+        <v>0.0673655893741668</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>2471</v>
+        <v>2528</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>資通</t>
+          <t>皇普</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>536.066294033266</v>
+        <v>525.4284128812789</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>53.8</v>
+        <v>22.4</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>56.78439422277883</v>
+        <v>52.40034391656715</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.10198851014008</v>
+        <v>37.92061796762138</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.36254739652349</v>
+        <v>0.5480372620402141</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0673655893741668</v>
+        <v>0.1668171948882068</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>2528</v>
+        <v>2514</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>皇普</t>
+          <t>龍邦</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>525.4284128812789</v>
+        <v>521.5046965365601</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>22.4</v>
+        <v>13.7</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>52.40034391656715</v>
+        <v>55.70404117751239</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>37.92061796762138</v>
+        <v>35.58049108013633</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5480372620402141</v>
+        <v>0.4409470255660603</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.1668171948882068</v>
+        <v>0.0315189844480954</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>2514</v>
+        <v>2498</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>龍邦</t>
+          <t>宏達電</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>521.5046965365601</v>
+        <v>521.3455023028052</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>13.7</v>
+        <v>46.4</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>55.70404117751239</v>
+        <v>54.95786116163075</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>35.58049108013633</v>
+        <v>20.80755145566917</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.4409470255660603</v>
+        <v>0.7052144963461026</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0315189844480954</v>
+        <v>-0.0117856130770517</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>2498</v>
+        <v>3067</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>宏達電</t>
+          <t>全域</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>521.3455023028052</v>
+        <v>520.5054187692949</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>46.4</v>
+        <v>19.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>54.95786116163075</v>
+        <v>52.72157047387073</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.80755145566917</v>
+        <v>10.14617598158262</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7052144963461026</v>
+        <v>0.1415096936893284</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0117856130770517</v>
+        <v>-0.843760396357323</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>3055</v>
+        <v>3066</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>蔚華科</t>
+          <t>李洲</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>510.4602976298158</v>
+        <v>516.0802898783218</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>91.09999999999999</v>
+        <v>21.3</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.8580624753936</v>
+        <v>54.73468314497952</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>25.3292875070314</v>
+        <v>25.2226773428355</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.057447924573928</v>
+        <v>0.6650191096340063</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-2.026504678082813</v>
+        <v>-0.1184694184130912</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>3027</v>
+        <v>3055</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>盛達</t>
+          <t>蔚華科</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>501.2090102864494</v>
+        <v>510.4602976298158</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>21</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>54.88043012733355</v>
+        <v>47.8580624753936</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>25.12152001021384</v>
+        <v>25.3292875070314</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.2954028292514639</v>
+        <v>1.057447924573928</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0247838618608249</v>
+        <v>-2.026504678082813</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>2474</v>
+        <v>3027</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>盛達</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>496.0461690276916</v>
+        <v>501.2090102864494</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>202.5</v>
+        <v>21</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>45.89433289451121</v>
+        <v>54.88043012733355</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>22.87214668738279</v>
+        <v>25.12152001021384</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4559407563767022</v>
+        <v>0.2954028292514639</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-2.423902351906267</v>
+        <v>-0.0247838618608249</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>2454</v>
+        <v>3081</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>494.4825871473993</v>
+        <v>497.0715395258266</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>4390</v>
+        <v>2440</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,49 +5428,49 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>58.51988983633969</v>
+        <v>48.52652305533513</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46.67906972718947</v>
+        <v>17.1627303013265</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.8839722324536161</v>
+        <v>0.943030251383168</v>
       </c>
       <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M94" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-55.13769282263053</v>
+        <v>-33.7363695881854</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>2516</v>
+        <v>2474</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>新建</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>494.0634718456995</v>
+        <v>496.0461690276916</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>13.35</v>
+        <v>202.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>55.50583788576475</v>
+        <v>45.89433289451121</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>28.69970685194804</v>
+        <v>22.87214668738279</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4247716198760989</v>
+        <v>0.4559407563767022</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1102507512718542</v>
+        <v>-2.423902351906267</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>2605</v>
+        <v>2454</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>新興</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>493.2089710780389</v>
+        <v>494.4825871473993</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>31</v>
+        <v>4390</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.70099420881274</v>
+        <v>58.51988983633969</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>20.19852183437649</v>
+        <v>46.67906972718947</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.844365855797992</v>
+        <v>0.8839722324536161</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1518246159049948</v>
+        <v>-55.13769282263053</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3017</v>
+        <v>2516</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>新建</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>491.1643267035171</v>
+        <v>494.0634718456995</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>2400</v>
+        <v>13.35</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.35124254034461</v>
+        <v>55.50583788576475</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>19.34223575176379</v>
+        <v>28.69970685194804</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.6790487435159648</v>
+        <v>0.4247716198760989</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-32.56079971584192</v>
+        <v>0.1102507512718542</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3011</v>
+        <v>2605</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>今皓</t>
+          <t>新興</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>490.6227332719174</v>
+        <v>493.2089710780389</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>14.55</v>
+        <v>31</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>55.4614313676591</v>
+        <v>44.70099420881274</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>17.57288357218821</v>
+        <v>20.19852183437649</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4816881809593169</v>
+        <v>1.844365855797992</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.011149028851373</v>
+        <v>0.1518246159049948</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>3067</v>
+        <v>3017</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>全域</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>490.5054187692949</v>
+        <v>491.1643267035171</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>19.5</v>
+        <v>2400</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.72157047387073</v>
+        <v>44.35124254034461</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>10.14617598158262</v>
+        <v>19.34223575176379</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.1415096936893284</v>
+        <v>0.6790487435159648</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.843760396357323</v>
+        <v>-32.56079971584192</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>3013</v>
+        <v>3011</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>晟銘電</t>
+          <t>今皓</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>483.2524636485568</v>
+        <v>490.6227332719174</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>113</v>
+        <v>14.55</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>49.10256811960608</v>
+        <v>55.4614313676591</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.60780176554292</v>
+        <v>17.57288357218821</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.316240191532108</v>
+        <v>0.4816881809593169</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.368932832345157</v>
+        <v>0.011149028851373</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>2545</v>
+        <v>3013</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>皇翔</t>
+          <t>晟銘電</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>479.5272303918396</v>
+        <v>483.2524636485568</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>38.55</v>
+        <v>113</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>56.12448522488982</v>
+        <v>49.10256811960608</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>19.73014715116805</v>
+        <v>20.60780176554292</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.146529711042625</v>
+        <v>0.316240191532108</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1147646766386572</v>
+        <v>-1.368932832345157</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>2504</v>
+        <v>2545</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>皇翔</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>470.6184965826384</v>
+        <v>479.5272303918396</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>33.6</v>
+        <v>38.55</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,49 +5852,49 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>35.37861695832402</v>
+        <v>56.12448522488982</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>27.48261570666323</v>
+        <v>19.73014715116805</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.461849658263847</v>
+        <v>1.146529711042625</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1933885594582499</v>
+        <v>0.1147646766386572</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>2450</v>
+        <v>2504</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>神腦</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>454.381088418335</v>
+        <v>470.6184965826384</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>29.15</v>
+        <v>33.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,49 +5905,49 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.13015024586505</v>
+        <v>35.37861695832402</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>25.45682858624</v>
+        <v>27.48261570666323</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.642310242872694</v>
+        <v>1.461849658263847</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M103" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.158804377938092</v>
+        <v>-0.1933885594582499</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>2543</v>
+        <v>2450</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>皇昌</t>
+          <t>神腦</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>449.6254598073222</v>
+        <v>454.381088418335</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>44.1</v>
+        <v>29.15</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>43.19751655979938</v>
+        <v>39.13015024586505</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>21.90318318521826</v>
+        <v>25.45682858624</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.8312534801722543</v>
+        <v>0.642310242872694</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.0929511045406794</v>
+        <v>-0.158804377938092</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>3057</v>
+        <v>2543</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>喬鼎</t>
+          <t>皇昌</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>442.8822813532183</v>
+        <v>449.6254598073222</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>19.7</v>
+        <v>44.1</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.96255274877395</v>
+        <v>43.19751655979938</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>25.49525962505037</v>
+        <v>21.90318318521826</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5490752601973248</v>
+        <v>0.8312534801722543</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2565737304290051</v>
+        <v>0.0929511045406794</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>3030</v>
+        <v>3057</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>喬鼎</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>440.7012123576859</v>
+        <v>442.8822813532183</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>340.5</v>
+        <v>19.7</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,49 +6064,49 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.913647380482</v>
+        <v>46.96255274877395</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.77826149250753</v>
+        <v>25.49525962505037</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4111499783073873</v>
+        <v>0.5490752601973248</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-5.069905926107431</v>
+        <v>-0.2565737304290051</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>2601</v>
+        <v>3030</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>益航</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>438.2818402124539</v>
+        <v>440.7012123576859</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>5.81</v>
+        <v>340.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,49 +6117,49 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>55.61448281537816</v>
+        <v>44.913647380482</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>30.77677406004436</v>
+        <v>22.77826149250753</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4556641451655265</v>
+        <v>0.4111499783073873</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0072666096247474</v>
+        <v>-5.069905926107431</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>2466</v>
+        <v>2601</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>冠西電</t>
+          <t>益航</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>435.3792977884637</v>
+        <v>438.2818402124539</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>50.1</v>
+        <v>5.81</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>57.08721767888262</v>
+        <v>55.61448281537816</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>19.87086203280673</v>
+        <v>30.77677406004436</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.031854814620986</v>
+        <v>0.4556641451655265</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.7871978962183717</v>
+        <v>-0.0072666096247474</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>3058</v>
+        <v>2466</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>立德</t>
+          <t>冠西電</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>429.4816788824587</v>
+        <v>435.3792977884637</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>9.4</v>
+        <v>50.1</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>54.0097618267045</v>
+        <v>57.08721767888262</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>31.04335446468876</v>
+        <v>19.87086203280673</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4811003707805066</v>
+        <v>1.031854814620986</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0086834295662741</v>
+        <v>0.7871978962183717</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>2449</v>
+        <v>3128</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>昇銳</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>421.1820348704577</v>
+        <v>434.5377779883393</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>308.5</v>
+        <v>24.55</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>54.3639287453657</v>
+        <v>54.60536924753645</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.66882119262498</v>
+        <v>16.08407236821269</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.218697556960886</v>
+        <v>0.4389775481274863</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-1.351777322297684</v>
+        <v>0.0180322358113691</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>2614</v>
+        <v>3058</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>東森</t>
+          <t>立德</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>420.1485012375175</v>
+        <v>429.4816788824587</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>18.85</v>
+        <v>9.4</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>47.10398842141253</v>
+        <v>54.0097618267045</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>24.46844426582353</v>
+        <v>31.04335446468876</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8140753818577456</v>
+        <v>0.4811003707805066</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0626236749773483</v>
+        <v>-0.0086834295662741</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>3115</v>
+        <v>2449</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>富榮綱</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>418.2024288983857</v>
+        <v>421.1820348704577</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>9</v>
+        <v>308.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>52.42567238311998</v>
+        <v>54.3639287453657</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>20.40873301975279</v>
+        <v>14.66882119262498</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.1388157469257278</v>
+        <v>1.218697556960886</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.4160674345405221</v>
+        <v>-1.351777322297684</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>3049</v>
+        <v>2614</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>精金</t>
+          <t>東森</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>417.6798780425585</v>
+        <v>420.1485012375175</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>14.45</v>
+        <v>18.85</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>53.49501267681142</v>
+        <v>47.10398842141253</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.43101673661339</v>
+        <v>24.46844426582353</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4460610814992419</v>
+        <v>0.8140753818577456</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0391614907524269</v>
+        <v>0.0626236749773483</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>3128</v>
+        <v>3049</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>昇銳</t>
+          <t>精金</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>404.5377779883393</v>
+        <v>417.6798780425585</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>24.55</v>
+        <v>14.45</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>54.60536924753645</v>
+        <v>53.49501267681142</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.08407236821269</v>
+        <v>19.43101673661339</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4389775481274863</v>
+        <v>0.4460610814992419</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,11 +6506,11 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0180322358113691</v>
+        <v>-0.0391614907524269</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>2457</v>
+        <v>3078</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>飛宏</t>
+          <t>僑威</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>381.2377974238515</v>
+        <v>382.3953391730915</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>28.8</v>
+        <v>55.3</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>53.88552610673552</v>
+        <v>46.45911244444417</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>17.36728610538509</v>
+        <v>16.37051922895258</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.5237797423851502</v>
+        <v>0.621410710195622</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0641863995551583</v>
+        <v>-0.1935126123807065</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>2608</v>
+        <v>2457</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>嘉里大榮</t>
+          <t>飛宏</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>378.6834026355133</v>
+        <v>381.2377974238515</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>40.10922201114432</v>
+        <v>53.88552610673552</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>22.82480391299582</v>
+        <v>17.36728610538509</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4288736777912069</v>
+        <v>0.5237797423851502</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0548814286322098</v>
+        <v>-0.0641863995551583</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>2496</v>
+        <v>2608</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>卓越</t>
+          <t>嘉里大榮</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>376.5798299276809</v>
+        <v>378.6834026355133</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>65</v>
+        <v>29.1</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>50.92781975136588</v>
+        <v>40.10922201114432</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.85837970114459</v>
+        <v>22.82480391299582</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.002659900533579</v>
+        <v>0.4288736777912069</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0349715740007585</v>
+        <v>-0.0548814286322098</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>2603</v>
+        <v>3115</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>富榮綱</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>376.555076908771</v>
+        <v>378.2024288983857</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>193</v>
+        <v>9</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>32.36389698352703</v>
+        <v>52.42567238311998</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>28.89926613131723</v>
+        <v>20.40873301975279</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5555076908770989</v>
+        <v>0.1388157469257278</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-3.935773670120802</v>
+        <v>-0.4160674345405221</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>2468</v>
+        <v>2496</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>華經</t>
+          <t>卓越</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>357.8255879838446</v>
+        <v>376.5798299276809</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>50.45969020715182</v>
+        <v>50.92781975136588</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>26.51293279916833</v>
+        <v>18.85837970114459</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.1825587983844565</v>
+        <v>1.002659900533579</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.3658778000222202</v>
+        <v>0.0349715740007585</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>2548</v>
+        <v>2603</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>華固</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>353.8509533722037</v>
+        <v>376.555076908771</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>103.5</v>
+        <v>193</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>38.57742364498123</v>
+        <v>32.36389698352703</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>22.23692185069009</v>
+        <v>28.89926613131723</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.9069458675908976</v>
+        <v>0.5555076908770989</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.1960817814121123</v>
+        <v>-3.935773670120802</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>3078</v>
+        <v>2468</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>僑威</t>
+          <t>華經</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>352.3953391730915</v>
+        <v>357.8255879838446</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>55.3</v>
+        <v>38</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>46.45911244444417</v>
+        <v>50.45969020715182</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>16.37051922895258</v>
+        <v>26.51293279916833</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.621410710195622</v>
+        <v>0.1825587983844565</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>1</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.1935126123807065</v>
+        <v>-0.3658778000222202</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>3062</v>
+        <v>2548</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>建漢</t>
+          <t>華固</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>346.307529388599</v>
+        <v>353.8509533722037</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>25.95</v>
+        <v>103.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>42.75538765518249</v>
+        <v>38.57742364498123</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>23.80833276644607</v>
+        <v>22.23692185069009</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5276325044569889</v>
+        <v>0.9069458675908976</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.3570563725118123</v>
+        <v>0.1960817814121123</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>3122</v>
+        <v>3062</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>笙泉</t>
+          <t>建漢</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>346.2308825459756</v>
+        <v>346.307529388599</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>31.05</v>
+        <v>25.95</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>47.36357377590732</v>
+        <v>42.75538765518249</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>21.34963085384528</v>
+        <v>23.80833276644607</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.7234673795538077</v>
+        <v>0.5276325044569889</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,11 +7248,11 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.03353966517324</v>
+        <v>-0.3570563725118123</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
@@ -7523,21 +7523,21 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>2607</v>
+        <v>3122</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>榮運</t>
+          <t>笙泉</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>322.1202747069533</v>
+        <v>326.2308825459756</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>49.55</v>
+        <v>31.05</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>54.91919344712848</v>
+        <v>47.36357377590732</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>18.07427971896576</v>
+        <v>21.34963085384528</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>1.051616344839786</v>
+        <v>0.7234673795538077</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>0</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.1422889751072962</v>
+        <v>-0.03353966517324</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>2640</v>
+        <v>2607</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>榮運</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>309.8654085089972</v>
+        <v>322.1202747069533</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>152.5</v>
+        <v>49.55</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>36.75754346674893</v>
+        <v>54.91919344712848</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>21.92058011167149</v>
+        <v>18.07427971896576</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>1.266820549943014</v>
+        <v>1.051616344839786</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,11 +7619,11 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-0.3016573245317913</v>
+        <v>0.1422889751072962</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -7682,21 +7682,21 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>2459</v>
+        <v>2640</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>敦吉</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>287.4120800607698</v>
+        <v>289.8654085089972</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>64.40000000000001</v>
+        <v>152.5</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>35.72724599235582</v>
+        <v>36.75754346674893</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>17.32940918423913</v>
+        <v>21.92058011167149</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.6412080060769787</v>
+        <v>1.266820549943014</v>
       </c>
       <c r="K137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>-0.548233147964573</v>
+        <v>-0.3016573245317913</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>3095</v>
+        <v>2459</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>及成</t>
+          <t>敦吉</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>283.5738961767473</v>
+        <v>287.4120800607698</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>39</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>38.18739173332319</v>
+        <v>35.72724599235582</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>24.62560859014166</v>
+        <v>17.32940918423913</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.2448988594809291</v>
+        <v>0.6412080060769787</v>
       </c>
       <c r="K138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>-0.5662200973661875</v>
+        <v>-0.548233147964573</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>3085</v>
+        <v>3031</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>新零售</t>
+          <t>佰鴻</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>281.4861284638784</v>
+        <v>276.0609864382289</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>12.15</v>
+        <v>28</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,16 +7813,16 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>45.84455072461628</v>
+        <v>41.04633204222425</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>12.09540178265259</v>
+        <v>11.80814907104943</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.0991669121132266</v>
+        <v>0.7140536309893973</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>-0.0600208212932223</v>
+        <v>-0.3542135398777536</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>3031</v>
+        <v>2485</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>佰鴻</t>
+          <t>兆赫</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>276.0609864382289</v>
+        <v>271.2459303720552</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>28</v>
+        <v>61.7</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>41.04633204222425</v>
+        <v>41.30752984620423</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>11.80814907104943</v>
+        <v>12.78814518664985</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.7140536309893973</v>
+        <v>0.3755113246021064</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.3542135398777536</v>
+        <v>-0.7838824934631243</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7894,21 +7894,21 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>2485</v>
+        <v>2530</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>兆赫</t>
+          <t>華建</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>271.2459303720552</v>
+        <v>251.335528039524</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>61.7</v>
+        <v>20</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,13 +7919,13 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>41.30752984620423</v>
+        <v>49.11597123845337</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>12.78814518664985</v>
+        <v>28.1065895687722</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.3755113246021064</v>
+        <v>0.8005158406788301</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>-0.7838824934631243</v>
+        <v>0.2151297257651928</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>2530</v>
+        <v>3095</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>華建</t>
+          <t>及成</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>251.335528039524</v>
+        <v>243.5738961767472</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,13 +7972,13 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>49.11597123845337</v>
+        <v>38.18739173332319</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>28.1065895687722</v>
+        <v>24.62560859014166</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.8005158406788301</v>
+        <v>0.2448988594809291</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>0</v>
@@ -7990,31 +7990,31 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>0.2151297257651928</v>
+        <v>-0.5662200973661875</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>3024</v>
+        <v>3085</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>憶聲</t>
+          <t>新零售</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>235.3394181176887</v>
+        <v>241.4861284638784</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>12.2</v>
+        <v>12.15</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,13 +8025,13 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>35.51371811223112</v>
+        <v>45.84455072461628</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>36.845447656358</v>
+        <v>12.09540178265259</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.4205219825173399</v>
+        <v>0.0991669121132266</v>
       </c>
       <c r="K143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-0.2296857404606017</v>
+        <v>-0.0600208212932223</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>2477</v>
+        <v>3024</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>美隆電</t>
+          <t>憶聲</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>214.254000821496</v>
+        <v>235.3394181176887</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>21.9</v>
+        <v>12.2</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>48.94220732140914</v>
+        <v>35.51371811223112</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>15.74389770650194</v>
+        <v>36.845447656358</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.4052149383890671</v>
+        <v>0.4205219825173399</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>0</v>
@@ -8096,31 +8096,31 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.0258268630609151</v>
+        <v>-0.2296857404606017</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>3073</v>
+        <v>2477</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>天方能源</t>
+          <t>美隆電</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>194.6453366424758</v>
+        <v>214.254000821496</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>48.67269280970289</v>
+        <v>48.94220732140914</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>16.02773906451728</v>
+        <v>15.74389770650194</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.591513880165953</v>
+        <v>0.4052149383890671</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>0</v>
@@ -8149,11 +8149,11 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.08410592219345869</v>
+        <v>-0.0258268630609151</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -8212,52 +8212,105 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
+        <v>3073</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>天方能源</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>154.6453366424758</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>48.67269280970289</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>16.02773906451728</v>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.591513880165953</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N147" s="2" t="n">
+        <v>0.08410592219345869</v>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
         <v>2612</v>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>中航</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D147" s="2" t="n">
+      <c r="C148" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D148" s="2" t="n">
         <v>151.486479085618</v>
       </c>
-      <c r="E147" s="2" t="n">
+      <c r="E148" s="2" t="n">
         <v>53.7</v>
       </c>
-      <c r="F147" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G147" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H147" s="2" t="n">
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H148" s="2" t="n">
         <v>40.23398912073363</v>
       </c>
-      <c r="I147" s="2" t="n">
+      <c r="I148" s="2" t="n">
         <v>11.44012974929658</v>
       </c>
-      <c r="J147" s="2" t="n">
+      <c r="J148" s="2" t="n">
         <v>0.812982464007012</v>
       </c>
-      <c r="K147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N147" s="2" t="n">
+      <c r="K148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N148" s="2" t="n">
         <v>-0.2215870995835993</v>
       </c>
-      <c r="O147" s="2" t="inlineStr">
+      <c r="O148" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
